--- a/Simulacao_IR.xlsx
+++ b/Simulacao_IR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31CAFF3B-B58A-4848-8898-6F4C05746BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79E06DF-DBB1-4A6F-BDA8-73283FFF8CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3012" yWindow="2112" windowWidth="17280" windowHeight="8880" tabRatio="855" activeTab="3" xr2:uid="{F47EE19A-31A9-4CC6-8CB1-E847121EA0EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="0" xr2:uid="{F47EE19A-31A9-4CC6-8CB1-E847121EA0EC}"/>
   </bookViews>
   <sheets>
     <sheet name="TITULAR" sheetId="1" r:id="rId1"/>
@@ -642,14 +642,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3021,10 +3021,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1DE7DBEE-94CE-45BC-AD66-ED830059B598}" name="Tabela2" displayName="Tabela2" ref="C8:H52" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="C8:H52" xr:uid="{1DE7DBEE-94CE-45BC-AD66-ED830059B598}"/>
@@ -3541,11 +3537,11 @@
       <c r="D6" s="15"/>
     </row>
     <row r="7" spans="3:5" ht="16.8">
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <f>SUM(D11,D16,D21)</f>
         <v>31221341.350000001</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="26"/>
     </row>
     <row r="9" spans="3:5">
       <c r="C9" s="14" t="s">
@@ -3999,14 +3995,14 @@
       <c r="H4" s="23"/>
     </row>
     <row r="7" spans="3:8" ht="16.8">
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="3:8" ht="16.8">
       <c r="C8" s="17" t="s">
